--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/90.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/90.xlsx
@@ -426,13 +426,13 @@
         <v>-4.461126591351666</v>
       </c>
       <c r="E2">
-        <v>-14.43289631093613</v>
+        <v>-11.44529898301172</v>
       </c>
       <c r="F2">
-        <v>-3.802283564265699</v>
+        <v>-3.253286381529938</v>
       </c>
       <c r="G2">
-        <v>-9.424625328837497</v>
+        <v>-9.077206308901932</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.204272995159097</v>
       </c>
       <c r="E3">
-        <v>-15.07239835335132</v>
+        <v>-12.58640197736052</v>
       </c>
       <c r="F3">
-        <v>-3.56324572467686</v>
+        <v>-2.897859608378157</v>
       </c>
       <c r="G3">
-        <v>-9.125568233466588</v>
+        <v>-8.742892487874787</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.11198756801416</v>
       </c>
       <c r="E4">
-        <v>-15.6229204099898</v>
+        <v>-13.05563792556132</v>
       </c>
       <c r="F4">
-        <v>-3.450388121352052</v>
+        <v>-3.096289221146959</v>
       </c>
       <c r="G4">
-        <v>-9.837340657806013</v>
+        <v>-8.854926516800468</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.197530799511408</v>
       </c>
       <c r="E5">
-        <v>-15.6095206554011</v>
+        <v>-13.66061941061604</v>
       </c>
       <c r="F5">
-        <v>-3.632705988136404</v>
+        <v>-2.343298281797791</v>
       </c>
       <c r="G5">
-        <v>-9.343529937995822</v>
+        <v>-8.811168146083713</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.409542214801187</v>
       </c>
       <c r="E6">
-        <v>-15.94988529029161</v>
+        <v>-14.6568746353555</v>
       </c>
       <c r="F6">
-        <v>-3.620246514030896</v>
+        <v>-2.96895009888641</v>
       </c>
       <c r="G6">
-        <v>-9.380204151365735</v>
+        <v>-8.272782031388465</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.699805595494889</v>
       </c>
       <c r="E7">
-        <v>-17.17310310382151</v>
+        <v>-15.06550601591165</v>
       </c>
       <c r="F7">
-        <v>-3.117714944020368</v>
+        <v>-2.288397403809851</v>
       </c>
       <c r="G7">
-        <v>-9.448847306389318</v>
+        <v>-8.018520172747094</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.007566354842743</v>
       </c>
       <c r="E8">
-        <v>-17.64025595397877</v>
+        <v>-15.45770809276796</v>
       </c>
       <c r="F8">
-        <v>-2.912878737758315</v>
+        <v>-2.206601092987817</v>
       </c>
       <c r="G8">
-        <v>-9.985159689058998</v>
+        <v>-9.370107832627323</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.270729831042554</v>
       </c>
       <c r="E9">
-        <v>-18.1530241228153</v>
+        <v>-15.83948562245862</v>
       </c>
       <c r="F9">
-        <v>-2.660743581163812</v>
+        <v>-2.16610552413456</v>
       </c>
       <c r="G9">
-        <v>-9.067815452798801</v>
+        <v>-8.934020362490884</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.430173881444775</v>
       </c>
       <c r="E10">
-        <v>-18.01246481809122</v>
+        <v>-16.39986616701179</v>
       </c>
       <c r="F10">
-        <v>-2.867333441217592</v>
+        <v>-1.597758507236805</v>
       </c>
       <c r="G10">
-        <v>-9.01393451357116</v>
+        <v>-9.225202526119126</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.433512465593404</v>
       </c>
       <c r="E11">
-        <v>-19.43558758821572</v>
+        <v>-18.873708118766</v>
       </c>
       <c r="F11">
-        <v>-2.102462884944877</v>
+        <v>-1.416693960332889</v>
       </c>
       <c r="G11">
-        <v>-8.889162782551715</v>
+        <v>-7.775056814257855</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.248723683350608</v>
       </c>
       <c r="E12">
-        <v>-20.09437640142958</v>
+        <v>-17.1348420269307</v>
       </c>
       <c r="F12">
-        <v>-2.177465754696553</v>
+        <v>-1.568438443014717</v>
       </c>
       <c r="G12">
-        <v>-8.663030836339463</v>
+        <v>-8.236229223216251</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.861494805165697</v>
       </c>
       <c r="E13">
-        <v>-19.64933608985177</v>
+        <v>-18.06479133524985</v>
       </c>
       <c r="F13">
-        <v>-1.947610367767746</v>
+        <v>-0.9791536116438018</v>
       </c>
       <c r="G13">
-        <v>-8.519129583628455</v>
+        <v>-6.511340267739556</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.288902662679651</v>
       </c>
       <c r="E14">
-        <v>-20.57064054129028</v>
+        <v>-19.4871759641111</v>
       </c>
       <c r="F14">
-        <v>-1.581682381050675</v>
+        <v>-0.5608371852714822</v>
       </c>
       <c r="G14">
-        <v>-8.081230879191201</v>
+        <v>-7.256840368488514</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.567837394152864</v>
       </c>
       <c r="E15">
-        <v>-21.22481031101631</v>
+        <v>-19.15359951175808</v>
       </c>
       <c r="F15">
-        <v>-1.379441449861593</v>
+        <v>-0.279466457929977</v>
       </c>
       <c r="G15">
-        <v>-7.751320457496832</v>
+        <v>-7.785497661260009</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.756138587270585</v>
       </c>
       <c r="E16">
-        <v>-21.68645200830625</v>
+        <v>-19.89259212812179</v>
       </c>
       <c r="F16">
-        <v>-0.9903382283164007</v>
+        <v>-0.1442719275886808</v>
       </c>
       <c r="G16">
-        <v>-7.652391627479575</v>
+        <v>-7.46167390555841</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.919789724826783</v>
       </c>
       <c r="E17">
-        <v>-22.96344997915123</v>
+        <v>-20.44053748304991</v>
       </c>
       <c r="F17">
-        <v>-0.6983536294428253</v>
+        <v>0.3057378356147478</v>
       </c>
       <c r="G17">
-        <v>-6.905959659807734</v>
+        <v>-5.861750273173167</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.121911080592934</v>
       </c>
       <c r="E18">
-        <v>-23.29473049518236</v>
+        <v>-22.33898699891551</v>
       </c>
       <c r="F18">
-        <v>-0.3506985992641092</v>
+        <v>0.327494077081874</v>
       </c>
       <c r="G18">
-        <v>-6.564866835038777</v>
+        <v>-6.020039682422339</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4193549173557593</v>
       </c>
       <c r="E19">
-        <v>-24.01111696929978</v>
+        <v>-23.48646155619311</v>
       </c>
       <c r="F19">
-        <v>0.06347267662460157</v>
+        <v>0.4528873643132463</v>
       </c>
       <c r="G19">
-        <v>-6.118637109062093</v>
+        <v>-4.880661745677637</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.1521870554431617</v>
       </c>
       <c r="E20">
-        <v>-24.84810123471547</v>
+        <v>-22.76146645298711</v>
       </c>
       <c r="F20">
-        <v>0.2043655463297555</v>
+        <v>1.246779772543042</v>
       </c>
       <c r="G20">
-        <v>-5.211632001935707</v>
+        <v>-4.241909625922093</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5672749024576086</v>
       </c>
       <c r="E21">
-        <v>-25.43347895579099</v>
+        <v>-24.66966577339123</v>
       </c>
       <c r="F21">
-        <v>0.6209763642197108</v>
+        <v>0.897922781262864</v>
       </c>
       <c r="G21">
-        <v>-5.347632073131571</v>
+        <v>-3.869116919667341</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8221995656849146</v>
       </c>
       <c r="E22">
-        <v>-25.62243406223504</v>
+        <v>-23.59568834925812</v>
       </c>
       <c r="F22">
-        <v>0.7971717675299713</v>
+        <v>1.22901626195741</v>
       </c>
       <c r="G22">
-        <v>-5.231309487627696</v>
+        <v>-3.365469097621934</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.9219070809404493</v>
       </c>
       <c r="E23">
-        <v>-26.94642853633163</v>
+        <v>-24.48681957838352</v>
       </c>
       <c r="F23">
-        <v>0.3776127900534525</v>
+        <v>1.782443553563342</v>
       </c>
       <c r="G23">
-        <v>-4.518834881874549</v>
+        <v>-3.003392860980329</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.8818475148165439</v>
       </c>
       <c r="E24">
-        <v>-27.56485506071512</v>
+        <v>-25.75089328441062</v>
       </c>
       <c r="F24">
-        <v>1.156829013007849</v>
+        <v>1.449096913533182</v>
       </c>
       <c r="G24">
-        <v>-4.134039467155349</v>
+        <v>-3.56788109318096</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.7264267786146082</v>
       </c>
       <c r="E25">
-        <v>-27.52973221631163</v>
+        <v>-25.34249738450288</v>
       </c>
       <c r="F25">
-        <v>0.5581935703941335</v>
+        <v>1.16585987443317</v>
       </c>
       <c r="G25">
-        <v>-4.78508960531569</v>
+        <v>-3.311581595951174</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.4811258171455978</v>
       </c>
       <c r="E26">
-        <v>-27.59216628745538</v>
+        <v>-25.08830508150433</v>
       </c>
       <c r="F26">
-        <v>0.8565392025538062</v>
+        <v>1.932386337144081</v>
       </c>
       <c r="G26">
-        <v>-4.29073748394819</v>
+        <v>-3.697843716707446</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.1783264910762272</v>
       </c>
       <c r="E27">
-        <v>-28.97831859578125</v>
+        <v>-26.43475172973094</v>
       </c>
       <c r="F27">
-        <v>0.3427658585198857</v>
+        <v>1.037713093954892</v>
       </c>
       <c r="G27">
-        <v>-3.788861521544883</v>
+        <v>-4.063273361782804</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1546680925405632</v>
       </c>
       <c r="E28">
-        <v>-28.20146793671342</v>
+        <v>-25.68792938180797</v>
       </c>
       <c r="F28">
-        <v>0.3320053659575201</v>
+        <v>1.180624695020668</v>
       </c>
       <c r="G28">
-        <v>-3.92419550476418</v>
+        <v>-3.786266075291362</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4903013361365399</v>
       </c>
       <c r="E29">
-        <v>-28.22461749584063</v>
+        <v>-26.29839032041198</v>
       </c>
       <c r="F29">
-        <v>0.7156587583596943</v>
+        <v>1.049878497632405</v>
       </c>
       <c r="G29">
-        <v>-4.280477104131807</v>
+        <v>-4.548152596508188</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8070049018833912</v>
       </c>
       <c r="E30">
-        <v>-27.01031624763184</v>
+        <v>-24.86792689392105</v>
       </c>
       <c r="F30">
-        <v>0.3884370669058336</v>
+        <v>1.114747948945634</v>
       </c>
       <c r="G30">
-        <v>-4.094714026765404</v>
+        <v>-3.24388671395827</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.089474463453835</v>
       </c>
       <c r="E31">
-        <v>-27.97128560290354</v>
+        <v>-25.57821804202414</v>
       </c>
       <c r="F31">
-        <v>0.5622525706678511</v>
+        <v>0.8380384449796821</v>
       </c>
       <c r="G31">
-        <v>-3.801280945147381</v>
+        <v>-2.934690643968676</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.326674467290158</v>
       </c>
       <c r="E32">
-        <v>-28.0030890758594</v>
+        <v>-24.34625121671143</v>
       </c>
       <c r="F32">
-        <v>0.2354483763850013</v>
+        <v>1.242813549418438</v>
       </c>
       <c r="G32">
-        <v>-5.120243419062052</v>
+        <v>-3.584667822679079</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.518304363923209</v>
       </c>
       <c r="E33">
-        <v>-27.20532592382415</v>
+        <v>-24.86511924003629</v>
       </c>
       <c r="F33">
-        <v>0.4103407577706581</v>
+        <v>1.172372498953979</v>
       </c>
       <c r="G33">
-        <v>-4.234736875593147</v>
+        <v>-4.137566780331752</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.668092722506877</v>
       </c>
       <c r="E34">
-        <v>-26.52328792505491</v>
+        <v>-23.44869861144315</v>
       </c>
       <c r="F34">
-        <v>0.2745464894297352</v>
+        <v>0.9991608750286027</v>
       </c>
       <c r="G34">
-        <v>-4.247359734932331</v>
+        <v>-4.512341344408408</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.787133746187352</v>
       </c>
       <c r="E35">
-        <v>-26.61810964230152</v>
+        <v>-23.7782220795593</v>
       </c>
       <c r="F35">
-        <v>0.3945479332362856</v>
+        <v>1.01107279828086</v>
       </c>
       <c r="G35">
-        <v>-4.430156588008996</v>
+        <v>-4.070577360974128</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.888650883258412</v>
       </c>
       <c r="E36">
-        <v>-26.21448222552385</v>
+        <v>-24.07605528656977</v>
       </c>
       <c r="F36">
-        <v>0.3883840513920545</v>
+        <v>1.009591677364654</v>
       </c>
       <c r="G36">
-        <v>-4.366277766689726</v>
+        <v>-4.221300273307221</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.987195340544363</v>
       </c>
       <c r="E37">
-        <v>-25.74684935712177</v>
+        <v>-24.33132083790814</v>
       </c>
       <c r="F37">
-        <v>0.4418990707151109</v>
+        <v>1.2375650135543</v>
       </c>
       <c r="G37">
-        <v>-4.676825699961812</v>
+        <v>-4.362550298998197</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.099446593626505</v>
       </c>
       <c r="E38">
-        <v>-25.76360923942416</v>
+        <v>-24.47181674399611</v>
       </c>
       <c r="F38">
-        <v>0.4906750001267514</v>
+        <v>1.470651033354025</v>
       </c>
       <c r="G38">
-        <v>-4.735188787839656</v>
+        <v>-3.775976164480944</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.236822834155094</v>
       </c>
       <c r="E39">
-        <v>-25.48615416544821</v>
+        <v>-22.08742573931542</v>
       </c>
       <c r="F39">
-        <v>0.5746830519142605</v>
+        <v>1.17608027144891</v>
       </c>
       <c r="G39">
-        <v>-5.372848260815903</v>
+        <v>-3.596106161035303</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.411202511828313</v>
       </c>
       <c r="E40">
-        <v>-24.5480898317073</v>
+        <v>-22.55374535025527</v>
       </c>
       <c r="F40">
-        <v>0.6249533561205513</v>
+        <v>1.417040751779647</v>
       </c>
       <c r="G40">
-        <v>-4.751486615325417</v>
+        <v>-4.358770331761717</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.622170262786831</v>
       </c>
       <c r="E41">
-        <v>-24.55035406871114</v>
+        <v>-21.75364097715805</v>
       </c>
       <c r="F41">
-        <v>0.7372576100202887</v>
+        <v>1.287177594042768</v>
       </c>
       <c r="G41">
-        <v>-4.795983260893047</v>
+        <v>-4.222770260565852</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.868455925085915</v>
       </c>
       <c r="E42">
-        <v>-23.05629275325649</v>
+        <v>-21.38019583964151</v>
       </c>
       <c r="F42">
-        <v>0.8796274588046341</v>
+        <v>1.779357056620511</v>
       </c>
       <c r="G42">
-        <v>-5.061785175758985</v>
+        <v>-3.759894897618105</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.137461099136952</v>
       </c>
       <c r="E43">
-        <v>-23.68588196606889</v>
+        <v>-20.94194371060119</v>
       </c>
       <c r="F43">
-        <v>0.5497086030872582</v>
+        <v>1.172978863892829</v>
       </c>
       <c r="G43">
-        <v>-4.742118727773202</v>
+        <v>-4.74520635726064</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.415593286034115</v>
       </c>
       <c r="E44">
-        <v>-23.56655214749277</v>
+        <v>-20.43009482198822</v>
       </c>
       <c r="F44">
-        <v>0.5398096126238041</v>
+        <v>1.144183156236712</v>
       </c>
       <c r="G44">
-        <v>-4.606591152481898</v>
+        <v>-3.663827292800683</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.683123928864538</v>
       </c>
       <c r="E45">
-        <v>-22.78215705072816</v>
+        <v>-19.47009456015417</v>
       </c>
       <c r="F45">
-        <v>0.7894513833358799</v>
+        <v>1.094431410024574</v>
       </c>
       <c r="G45">
-        <v>-4.927520870768067</v>
+        <v>-3.513275003988681</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.919264847726897</v>
       </c>
       <c r="E46">
-        <v>-22.83857730838972</v>
+        <v>-20.32482138673191</v>
       </c>
       <c r="F46">
-        <v>0.5799970288032192</v>
+        <v>0.8871937666618047</v>
       </c>
       <c r="G46">
-        <v>-5.011106708773362</v>
+        <v>-3.543616459748866</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.10783203547917</v>
       </c>
       <c r="E47">
-        <v>-22.22064891614707</v>
+        <v>-18.83442813522347</v>
       </c>
       <c r="F47">
-        <v>0.7612603838838071</v>
+        <v>0.6845353383017113</v>
       </c>
       <c r="G47">
-        <v>-4.730529453225244</v>
+        <v>-3.99522410786148</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.234293114749192</v>
       </c>
       <c r="E48">
-        <v>-21.46345183427253</v>
+        <v>-19.7441713925204</v>
       </c>
       <c r="F48">
-        <v>0.7486576022176155</v>
+        <v>1.127211564888156</v>
       </c>
       <c r="G48">
-        <v>-5.130667859956408</v>
+        <v>-3.032438234224534</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.297439589292817</v>
       </c>
       <c r="E49">
-        <v>-21.56128045826023</v>
+        <v>-19.75584127003816</v>
       </c>
       <c r="F49">
-        <v>0.7547361622193582</v>
+        <v>1.262164211947834</v>
       </c>
       <c r="G49">
-        <v>-5.123593546274245</v>
+        <v>-3.644622303013253</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.297969546465538</v>
       </c>
       <c r="E50">
-        <v>-20.66515885077837</v>
+        <v>-17.5135764220882</v>
       </c>
       <c r="F50">
-        <v>0.5576973783198566</v>
+        <v>1.369126324466918</v>
       </c>
       <c r="G50">
-        <v>-5.150735811013972</v>
+        <v>-4.416227802489153</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.249768315380737</v>
       </c>
       <c r="E51">
-        <v>-20.9383481022391</v>
+        <v>-17.05918028321054</v>
       </c>
       <c r="F51">
-        <v>0.3986508369823515</v>
+        <v>1.2087444548761</v>
       </c>
       <c r="G51">
-        <v>-4.670463411358049</v>
+        <v>-3.857826236281292</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.166959561931714</v>
       </c>
       <c r="E52">
-        <v>-19.34601890081801</v>
+        <v>-16.47353538216857</v>
       </c>
       <c r="F52">
-        <v>0.5460339652884396</v>
+        <v>1.011679163219709</v>
       </c>
       <c r="G52">
-        <v>-4.860866136009506</v>
+        <v>-3.700173384014652</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.069926784945283</v>
       </c>
       <c r="E53">
-        <v>-19.45286824502899</v>
+        <v>-16.96610202845689</v>
       </c>
       <c r="F53">
-        <v>0.6415886303035709</v>
+        <v>1.299198861792195</v>
       </c>
       <c r="G53">
-        <v>-5.409574973730768</v>
+        <v>-4.447842372214403</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.977421463761873</v>
       </c>
       <c r="E54">
-        <v>-19.65625559813549</v>
+        <v>-16.18480893638753</v>
       </c>
       <c r="F54">
-        <v>0.5460463907994816</v>
+        <v>0.785521608376999</v>
       </c>
       <c r="G54">
-        <v>-5.144842737093209</v>
+        <v>-2.98814174317203</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.901787602703408</v>
       </c>
       <c r="E55">
-        <v>-18.48959389648739</v>
+        <v>-16.25960574157222</v>
       </c>
       <c r="F55">
-        <v>0.6117301272696628</v>
+        <v>0.7257515867954035</v>
       </c>
       <c r="G55">
-        <v>-4.793725780460149</v>
+        <v>-4.406072421762672</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.855960288996861</v>
       </c>
       <c r="E56">
-        <v>-19.0841191350584</v>
+        <v>-15.04427200128968</v>
       </c>
       <c r="F56">
-        <v>0.6765084581685841</v>
+        <v>0.802470005438277</v>
       </c>
       <c r="G56">
-        <v>-4.879729878754755</v>
+        <v>-3.841003413346019</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.83985565023493</v>
       </c>
       <c r="E57">
-        <v>-18.13500079626478</v>
+        <v>-16.37107412927103</v>
       </c>
       <c r="F57">
-        <v>0.4784300731785691</v>
+        <v>0.8018139384552597</v>
       </c>
       <c r="G57">
-        <v>-5.835792529416399</v>
+        <v>-3.645002924714149</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.855274617260628</v>
       </c>
       <c r="E58">
-        <v>-17.74123639587582</v>
+        <v>-15.36576195651622</v>
       </c>
       <c r="F58">
-        <v>0.7145537162443598</v>
+        <v>1.034793927227426</v>
       </c>
       <c r="G58">
-        <v>-5.395062130773344</v>
+        <v>-4.746961810794943</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.891563015590646</v>
       </c>
       <c r="E59">
-        <v>-16.74339167675966</v>
+        <v>-15.31154706569639</v>
       </c>
       <c r="F59">
-        <v>0.1629223251676962</v>
+        <v>0.8912660208139671</v>
       </c>
       <c r="G59">
-        <v>-5.703034305121266</v>
+        <v>-4.02944068628337</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.942798593998244</v>
       </c>
       <c r="E60">
-        <v>-17.26493149974905</v>
+        <v>-14.37378613971401</v>
       </c>
       <c r="F60">
-        <v>0.2307755558658093</v>
+        <v>0.8722185407539953</v>
       </c>
       <c r="G60">
-        <v>-5.78721404422882</v>
+        <v>-4.24051510675933</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.997567099221342</v>
       </c>
       <c r="E61">
-        <v>-16.9630362515537</v>
+        <v>-15.55680468947781</v>
       </c>
       <c r="F61">
-        <v>0.6074052210596466</v>
+        <v>0.8116731672833795</v>
       </c>
       <c r="G61">
-        <v>-5.805923569560774</v>
+        <v>-4.668383116889361</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.045450627566491</v>
       </c>
       <c r="E62">
-        <v>-16.99002595663941</v>
+        <v>-15.26730840311546</v>
       </c>
       <c r="F62">
-        <v>0.2314962355062449</v>
+        <v>1.214857806308761</v>
       </c>
       <c r="G62">
-        <v>-5.502312138665355</v>
+        <v>-5.012629195576944</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.077649034694089</v>
       </c>
       <c r="E63">
-        <v>-16.83304187668951</v>
+        <v>-14.38212306036213</v>
       </c>
       <c r="F63">
-        <v>0.0314074028296355</v>
+        <v>0.5592704480177728</v>
       </c>
       <c r="G63">
-        <v>-5.921534129986249</v>
+        <v>-4.542065930515418</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.082176364545649</v>
       </c>
       <c r="E64">
-        <v>-16.14415682522067</v>
+        <v>-14.76744185672678</v>
       </c>
       <c r="F64">
-        <v>0.3925697918784004</v>
+        <v>0.2861353493949003</v>
       </c>
       <c r="G64">
-        <v>-5.871397064557934</v>
+        <v>-5.469457267190634</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.055011241633848</v>
       </c>
       <c r="E65">
-        <v>-16.56268292148357</v>
+        <v>-15.03943559104949</v>
       </c>
       <c r="F65">
-        <v>0.1385699802601963</v>
+        <v>0.8926030058020855</v>
       </c>
       <c r="G65">
-        <v>-6.392307393227579</v>
+        <v>-6.292128417796173</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.988221407353732</v>
       </c>
       <c r="E66">
-        <v>-15.82539301134675</v>
+        <v>-15.13030847896141</v>
       </c>
       <c r="F66">
-        <v>0.5460687567193572</v>
+        <v>0.2111051435189323</v>
       </c>
       <c r="G66">
-        <v>-6.568968361988083</v>
+        <v>-5.634338650552731</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.883841090769913</v>
       </c>
       <c r="E67">
-        <v>-16.02450548499001</v>
+        <v>-14.39233024077542</v>
       </c>
       <c r="F67">
-        <v>0.1405572336595124</v>
+        <v>0.2695340382753954</v>
       </c>
       <c r="G67">
-        <v>-6.510247620960261</v>
+        <v>-6.399204520945532</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.742748099405385</v>
       </c>
       <c r="E68">
-        <v>-15.57589220742014</v>
+        <v>-14.93896233824131</v>
       </c>
       <c r="F68">
-        <v>0.03598330436269997</v>
+        <v>0.4054301958068627</v>
       </c>
       <c r="G68">
-        <v>-7.196794013950676</v>
+        <v>-6.422225571406597</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.573942345307525</v>
       </c>
       <c r="E69">
-        <v>-16.5063758756722</v>
+        <v>-13.81510377291371</v>
       </c>
       <c r="F69">
-        <v>0.09413635277403086</v>
+        <v>0.3739663167463291</v>
       </c>
       <c r="G69">
-        <v>-6.153234309184878</v>
+        <v>-6.402380743415074</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.388639143750942</v>
       </c>
       <c r="E70">
-        <v>-16.31990237298435</v>
+        <v>-13.70604000491297</v>
       </c>
       <c r="F70">
-        <v>0.3018262847387285</v>
+        <v>-0.3792565654756222</v>
       </c>
       <c r="G70">
-        <v>-6.678357726336851</v>
+        <v>-6.571219279977862</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.197590660630167</v>
       </c>
       <c r="E71">
-        <v>-16.70989455452492</v>
+        <v>-14.19390609518132</v>
       </c>
       <c r="F71">
-        <v>0.08151534702497759</v>
+        <v>0.3865210531031584</v>
       </c>
       <c r="G71">
-        <v>-7.291660691677341</v>
+        <v>-7.41185839984292</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.016214774006392</v>
       </c>
       <c r="E72">
-        <v>-16.65657630155861</v>
+        <v>-15.52213016400108</v>
       </c>
       <c r="F72">
-        <v>0.1151338097001927</v>
+        <v>0.1156830172882488</v>
       </c>
       <c r="G72">
-        <v>-7.094190215786839</v>
+        <v>-5.936736029471156</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.851881922403125</v>
       </c>
       <c r="E73">
-        <v>-16.28758718246561</v>
+        <v>-15.00031410409722</v>
       </c>
       <c r="F73">
-        <v>0.03138006670534312</v>
+        <v>0.4170820116946405</v>
       </c>
       <c r="G73">
-        <v>-7.087713084428495</v>
+        <v>-6.273379517805505</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.716572689350328</v>
       </c>
       <c r="E74">
-        <v>-16.38697812998596</v>
+        <v>-14.71475759012155</v>
       </c>
       <c r="F74">
-        <v>-0.04733388901087431</v>
+        <v>0.4532949210754237</v>
       </c>
       <c r="G74">
-        <v>-6.506018126370136</v>
+        <v>-5.971218386839361</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.612863199591313</v>
       </c>
       <c r="E75">
-        <v>-16.58343238938672</v>
+        <v>-16.02223219103816</v>
       </c>
       <c r="F75">
-        <v>0.3406949400128869</v>
+        <v>0.5022978231554313</v>
       </c>
       <c r="G75">
-        <v>-6.354117255497203</v>
+        <v>-5.424419220065696</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.547143242291563</v>
       </c>
       <c r="E76">
-        <v>-16.56472073478703</v>
+        <v>-15.09657587607827</v>
       </c>
       <c r="F76">
-        <v>-0.2217565860791438</v>
+        <v>-0.2603096333728356</v>
       </c>
       <c r="G76">
-        <v>-6.04254229987701</v>
+        <v>-5.891002363375616</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.519707499075688</v>
       </c>
       <c r="E77">
-        <v>-17.51013025336837</v>
+        <v>-16.82481363941757</v>
       </c>
       <c r="F77">
-        <v>0.07750936226503918</v>
+        <v>0.1700777627930783</v>
       </c>
       <c r="G77">
-        <v>-6.357352539954815</v>
+        <v>-6.848085473942247</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.527739840532286</v>
       </c>
       <c r="E78">
-        <v>-16.7610074406495</v>
+        <v>-16.3302046513518</v>
       </c>
       <c r="F78">
-        <v>-0.3971393609672579</v>
+        <v>0.05983614372631173</v>
       </c>
       <c r="G78">
-        <v>-5.968796845328491</v>
+        <v>-5.640930624665656</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.568620504788439</v>
       </c>
       <c r="E79">
-        <v>-17.74756720253854</v>
+        <v>-16.34394856996508</v>
       </c>
       <c r="F79">
-        <v>-0.2494605054983705</v>
+        <v>0.01899348893128211</v>
       </c>
       <c r="G79">
-        <v>-6.026572594547194</v>
+        <v>-6.52353984949757</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.632123328868593</v>
       </c>
       <c r="E80">
-        <v>-18.65480168523522</v>
+        <v>-16.48904087717084</v>
       </c>
       <c r="F80">
-        <v>-0.08264801975962002</v>
+        <v>-0.2304138538058014</v>
       </c>
       <c r="G80">
-        <v>-5.830516325148812</v>
+        <v>-5.957771940888756</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.712491108075926</v>
       </c>
       <c r="E81">
-        <v>-18.2839694772211</v>
+        <v>-18.26401249226929</v>
       </c>
       <c r="F81">
-        <v>-0.1951668208166825</v>
+        <v>-0.23554724660095</v>
       </c>
       <c r="G81">
-        <v>-5.793448365191765</v>
+        <v>-6.154573047581131</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.796770405393403</v>
       </c>
       <c r="E82">
-        <v>-19.27349086111116</v>
+        <v>-16.96516010586329</v>
       </c>
       <c r="F82">
-        <v>-0.4514902029997391</v>
+        <v>-0.220099022906142</v>
       </c>
       <c r="G82">
-        <v>-5.210588573479803</v>
+        <v>-5.275451761266906</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.877485201376324</v>
       </c>
       <c r="E83">
-        <v>-19.12646942397813</v>
+        <v>-19.05861929792121</v>
       </c>
       <c r="F83">
-        <v>-0.4744633161815778</v>
+        <v>-0.117279575768459</v>
       </c>
       <c r="G83">
-        <v>-5.438915656915323</v>
+        <v>-4.407040382122708</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.944000612729402</v>
       </c>
       <c r="E84">
-        <v>-21.33352991499246</v>
+        <v>-19.45098892831581</v>
       </c>
       <c r="F84">
-        <v>-0.2551745838428814</v>
+        <v>-0.07839352477884176</v>
       </c>
       <c r="G84">
-        <v>-5.512930171631718</v>
+        <v>-4.404789464132929</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.989475685204566</v>
       </c>
       <c r="E85">
-        <v>-22.20038852343675</v>
+        <v>-20.48169678330562</v>
       </c>
       <c r="F85">
-        <v>-0.3074984108407122</v>
+        <v>0.1389120959975526</v>
       </c>
       <c r="G85">
-        <v>-4.625595987754202</v>
+        <v>-4.377712823824392</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.011283826821912</v>
       </c>
       <c r="E86">
-        <v>-22.13709857070555</v>
+        <v>-21.37843426325252</v>
       </c>
       <c r="F86">
-        <v>-0.01486851376035608</v>
+        <v>-0.2780565766104122</v>
       </c>
       <c r="G86">
-        <v>-4.701087052172347</v>
+        <v>-4.286921423274556</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.007425740161467</v>
       </c>
       <c r="E87">
-        <v>-23.63046250116302</v>
+        <v>-21.99853179454485</v>
       </c>
       <c r="F87">
-        <v>-0.07437842797747256</v>
+        <v>0.1116215319123228</v>
       </c>
       <c r="G87">
-        <v>-4.497798970456949</v>
+        <v>-4.859127088583001</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.984581290212965</v>
       </c>
       <c r="E88">
-        <v>-24.1331050021184</v>
+        <v>-23.83725073824928</v>
       </c>
       <c r="F88">
-        <v>-0.2309622330264547</v>
+        <v>0.3015868865593195</v>
       </c>
       <c r="G88">
-        <v>-4.88401187288983</v>
+        <v>-4.206666025152098</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.946941436017011</v>
       </c>
       <c r="E89">
-        <v>-26.29950432501786</v>
+        <v>-25.35600129399375</v>
       </c>
       <c r="F89">
-        <v>-0.4222902520510565</v>
+        <v>0.213506580619648</v>
       </c>
       <c r="G89">
-        <v>-4.175281140936009</v>
+        <v>-4.074084986821174</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.906258543638307</v>
       </c>
       <c r="E90">
-        <v>-26.71443481291868</v>
+        <v>-25.62726141552721</v>
       </c>
       <c r="F90">
-        <v>0.2765917285472472</v>
+        <v>0.1228790449163681</v>
       </c>
       <c r="G90">
-        <v>-4.412001589120589</v>
+        <v>-3.863656966992425</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.870596494831859</v>
       </c>
       <c r="E91">
-        <v>-29.11585287986821</v>
+        <v>-27.53741250822864</v>
       </c>
       <c r="F91">
-        <v>-0.1773792875763687</v>
+        <v>-0.02125025623152347</v>
       </c>
       <c r="G91">
-        <v>-4.10105662803981</v>
+        <v>-4.920574524726722</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.850960328873464</v>
       </c>
       <c r="E92">
-        <v>-29.65434730954232</v>
+        <v>-28.39213480633237</v>
       </c>
       <c r="F92">
-        <v>-0.04402870307370427</v>
+        <v>-0.006712408312392146</v>
       </c>
       <c r="G92">
-        <v>-4.614124837182383</v>
+        <v>-4.161575478482209</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.856723002620378</v>
       </c>
       <c r="E93">
-        <v>-31.6302450521241</v>
+        <v>-29.58328423117695</v>
       </c>
       <c r="F93">
-        <v>-0.266554695222541</v>
+        <v>0.1575694150108058</v>
       </c>
       <c r="G93">
-        <v>-4.517325519957205</v>
+        <v>-4.346705280087638</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.891188073545504</v>
       </c>
       <c r="E94">
-        <v>-33.42683560213518</v>
+        <v>-32.39165361482578</v>
       </c>
       <c r="F94">
-        <v>-0.07523495987196725</v>
+        <v>-0.05801320156776553</v>
       </c>
       <c r="G94">
-        <v>-4.466082682863356</v>
+        <v>-4.131952610243541</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.959681317752966</v>
       </c>
       <c r="E95">
-        <v>-35.33754369713955</v>
+        <v>-35.86603246349371</v>
       </c>
       <c r="F95">
-        <v>-0.2741110626708781</v>
+        <v>-0.4727303715749212</v>
       </c>
       <c r="G95">
-        <v>-4.379907961047659</v>
+        <v>-5.419517075055886</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.057192830118784</v>
       </c>
       <c r="E96">
-        <v>-37.18968277356571</v>
+        <v>-37.14951973759169</v>
       </c>
       <c r="F96">
-        <v>-0.3389573196968291</v>
+        <v>-0.1637476735959</v>
       </c>
       <c r="G96">
-        <v>-4.273576695192294</v>
+        <v>-4.986848637784386</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.179765979863245</v>
       </c>
       <c r="E97">
-        <v>-39.96359499849019</v>
+        <v>-38.48845138320258</v>
       </c>
       <c r="F97">
-        <v>-0.3666090519696794</v>
+        <v>-0.4606328940244372</v>
       </c>
       <c r="G97">
-        <v>-4.554035826764272</v>
+        <v>-5.379797888078808</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.31740232018983</v>
       </c>
       <c r="E98">
-        <v>-42.47021857358592</v>
+        <v>-41.54419545223141</v>
       </c>
       <c r="F98">
-        <v>-0.4470311012704694</v>
+        <v>-0.2171094449494386</v>
       </c>
       <c r="G98">
-        <v>-5.121112942775305</v>
+        <v>-4.406177420852575</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.458861328435667</v>
       </c>
       <c r="E99">
-        <v>-43.96859326053288</v>
+        <v>-45.40008238638654</v>
       </c>
       <c r="F99">
-        <v>-0.5834068835281576</v>
+        <v>-0.7526274333068461</v>
       </c>
       <c r="G99">
-        <v>-5.434069292672023</v>
+        <v>-5.710226742779569</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.59816694896243</v>
       </c>
       <c r="E100">
-        <v>-46.17513071279932</v>
+        <v>-45.95449213796061</v>
       </c>
       <c r="F100">
-        <v>-0.5582427385659142</v>
+        <v>-0.7014624923055319</v>
       </c>
       <c r="G100">
-        <v>-5.838332194903409</v>
+        <v>-5.050195901211026</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.71766242157962</v>
       </c>
       <c r="E101">
-        <v>-49.04610511748569</v>
+        <v>-49.29674596474374</v>
       </c>
       <c r="F101">
-        <v>-0.6045782976089074</v>
+        <v>-0.955722411288215</v>
       </c>
       <c r="G101">
-        <v>-5.712018289751025</v>
+        <v>-6.100744607898441</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.828383913981478</v>
       </c>
       <c r="E102">
-        <v>-51.67212190979366</v>
+        <v>-51.7378561063705</v>
       </c>
       <c r="F102">
-        <v>-0.9781612274952479</v>
+        <v>-1.358231102512911</v>
       </c>
       <c r="G102">
-        <v>-6.901110014342875</v>
+        <v>-5.316040471957237</v>
       </c>
     </row>
   </sheetData>
